--- a/config/templates/OAS-K_Configuration_Template.xlsx
+++ b/config/templates/OAS-K_Configuration_Template.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HRIS_Assisted_Steps" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison_Settings" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attachment_Consolidation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Att_Data_Repair" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Global_Settings'!$A$3:$D$6</definedName>
@@ -42,6 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'HRIS_Assisted_Steps'!$A$3:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Comparison_Settings'!$A$3:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Attachment_Consolidation'!$A$3:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Att_Data_Repair'!$A$3:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +631,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
@@ -640,7 +642,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28T14:44:58</t>
+          <t>2026-08-04T11:28:54</t>
         </is>
       </c>
     </row>
@@ -7052,6 +7054,410 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Att Data Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Struktur key/value. Kolom required adalah informasi dan tidak diimpor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>setting_key</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>setting_value</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Aktifkan modul Att Data Repair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>minimum_duration_minutes</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Durasi minimum repair dalam menit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>weekday_default_in</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Jam masuk default Senin-Jumat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>weekday_default_out</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Jam keluar default Senin-Jumat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>saturday_default_in</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Jam masuk default Sabtu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>saturday_default_out</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Jam keluar default Sabtu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>saturday_missing_out_default</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Jam keluar saat Time_Out Sabtu kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>sunday_invalid_default_in</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Jam masuk default Minggu bila jam invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>sunday_invalid_default_out</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Jam keluar default Minggu bila jam invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>midnight_time_out_default</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Pengganti Time_Out saat nilainya 00:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>txt_max_rows</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Maksimum baris per TXT Att Data Repair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>generate_txt</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Buat TXT HRIS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>generate_excel_report</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Buat Excel report audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>use_global_period</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Gunakan periode global bila UI mendukung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>use_global_output</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Gunakan output root global bila UI mendukung.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D18"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Pilih nilai dari daftar yang tersedia." promptTitle="OAS-K" prompt="Gunakan salah satu nilai yang tersedia." type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Pilih nilai dari daftar yang tersedia." promptTitle="OAS-K" prompt="Gunakan salah satu nilai yang tersedia." type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Pilih nilai dari daftar yang tersedia." promptTitle="OAS-K" prompt="Gunakan salah satu nilai yang tersedia." type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Pilih nilai dari daftar yang tersedia." promptTitle="OAS-K" prompt="Gunakan salah satu nilai yang tersedia." type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Nilai tidak valid" error="Pilih nilai dari daftar yang tersedia." promptTitle="OAS-K" prompt="Gunakan salah satu nilai yang tersedia." type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
